--- a/request_forms/020_moodle_training_request_form--request_forms.xlsx
+++ b/request_forms/020_moodle_training_request_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -708,12 +708,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>Category 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>category_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>Category 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -754,12 +754,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>Assigned Tool 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -783,7 +783,7 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -876,7 +876,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -893,7 +893,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -910,7 +910,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_3_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -927,7 +927,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_3_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -944,7 +944,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
